--- a/output/pdf_financials_xlsx/CMCG.xlsx
+++ b/output/pdf_financials_xlsx/CMCG.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.019562</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.8636509999999999</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.019562</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.8636509999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.019562</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.898103</v>
+        <v>0.034452</v>
       </c>
     </row>
     <row r="49">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
